--- a/test-case-exports/MoneyRequest.xlsx
+++ b/test-case-exports/MoneyRequest.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -83,7 +83,7 @@
     <t>Skipped</t>
   </si>
   <si>
-    <t>test.skip(true, ...) in body — No pending request available — requires a request above the payer balance to be pre-created</t>
+    <t>Skipped: No pending request available — requires a request above the payer balance to be pre-created</t>
   </si>
   <si>
     <t>Money Request — Cancel Before Accept (MR-EC-01)</t>
@@ -98,7 +98,7 @@
     <t>MR-SEC-01: only the intended requested profile can act on a request</t>
   </si>
   <si>
-    <t>test.skip(true, ...) in body — Requires a third, unrelated business account to attempt Accept on a request not addressed to them — no such fixture account exists yet</t>
+    <t>Skipped: Requires a third, unrelated business account to attempt Accept on a request not addressed to them — no such fixture account exists yet</t>
   </si>
   <si>
     <t>Money Request — QR Generation &amp; Share (MR-UI-03)</t>
@@ -113,13 +113,13 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-26T17:32:41.286Z</t>
+    <t>2026-09-08T15:08:53.454Z</t>
   </si>
   <si>
     <t>Total test cases</t>
   </si>
   <si>
-    <t>Count per sub-folder (ui / functional / api / archive)</t>
+    <t>Count per sub-folder</t>
   </si>
   <si>
     <t>functional</t>
@@ -131,7 +131,10 @@
     <t>Archived</t>
   </si>
   <si>
-    <t>Spec files in this module</t>
+    <t>Gated behind an env flag</t>
+  </si>
+  <si>
+    <t>Spec files</t>
   </si>
 </sst>
 </file>
@@ -149,6 +152,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b/>
@@ -158,7 +162,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -168,11 +172,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -190,8 +189,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -536,15 +539,18 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,36 +579,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -631,36 +637,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -689,36 +695,36 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -747,37 +753,37 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="2" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -785,16 +791,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -813,11 +830,21 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -827,11 +854,21 @@
         <v>7</v>
       </c>
     </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="9" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -857,11 +894,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15">
         <v>1</v>
       </c>
     </row>
